--- a/entorno/mir-v2/archivos_de_prueba/Chaco_correctos/DISP_PENAL_2026_T1_Chaco.xlsx
+++ b/entorno/mir-v2/archivos_de_prueba/Chaco_correctos/DISP_PENAL_2026_T1_Chaco.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="CRC" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="CRSC" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="MPT" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="CAD" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Guardia Comisaría" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="INSTRUCCIONES" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="LISTAS" sheetId="7" state="hidden" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CRC" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CRSC" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MPT" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CAD" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guardia Comisaría" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INSTRUCCIONES" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTAS" sheetId="7" state="hidden" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/entorno/mir-v2/archivos_de_prueba/Chaco_correctos/DISP_PENAL_2026_T1_Chaco.xlsx
+++ b/entorno/mir-v2/archivos_de_prueba/Chaco_correctos/DISP_PENAL_2026_T1_Chaco.xlsx
@@ -1,19 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CRC" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CRSC" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MPT" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CAD" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Guardia Comisaría" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="INSTRUCCIONES" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LISTAS" sheetId="7" state="hidden" r:id="rId7"/>
+    <sheet name="CRC" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="CRSC" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="MPT" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="CAD" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Guardia Comisaría" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Listas" sheetId="6" state="hidden" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,10 +41,6 @@
     </font>
     <font>
       <b val="1"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="12"/>
     </font>
   </fonts>
   <fills count="5">
@@ -97,7 +92,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -110,10 +105,6 @@
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -193,304 +184,292 @@
 <file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>RUNAC</author>
+    <author>MIR</author>
   </authors>
   <commentList>
     <comment ref="A3" authorId="0" shapeId="0">
       <text>
         <t>Nombre del dispositvo
-Qué se espera: texto
-Máximo 120 caracteres.
-Campo obligatorio.</t>
+Obligatorio
+Qué va: Texto, hasta 120 caracteres.</t>
       </text>
     </comment>
     <comment ref="B3" authorId="0" shapeId="0">
       <text>
         <t>Dependencia institucional
-Qué se espera: texto
-Máximo 255 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 255 caracteres.</t>
       </text>
     </comment>
     <comment ref="C3" authorId="0" shapeId="0">
       <text>
         <t>Localidad
-Qué se espera: texto
-Máximo 120 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 120 caracteres.</t>
       </text>
     </comment>
     <comment ref="D3" authorId="0" shapeId="0">
       <text>
         <t>Dirección
-Qué se espera: texto
-Máximo 255 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 255 caracteres.</t>
       </text>
     </comment>
     <comment ref="E3" authorId="0" shapeId="0">
       <text>
         <t>Teléfono
-Qué se espera: texto
-Máximo 50 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 50 caracteres.</t>
       </text>
     </comment>
     <comment ref="F3" authorId="0" shapeId="0">
       <text>
         <t>Capacidad de alojamiento mujeres (plazas disponibles)
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.</t>
       </text>
     </comment>
     <comment ref="G3" authorId="0" shapeId="0">
       <text>
         <t>Capacidad de alojamiento varones (plazas disponibles)
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.</t>
       </text>
     </comment>
     <comment ref="H3" authorId="0" shapeId="0">
       <text>
         <t>¿Cuenta con Proyecto Institucional?
-Qué se espera: texto
-Máximo 38 caracteres.
-Elegir de la lista "Cuenta con Proyecto Institucional".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, es una herramienta de gestión, Sí, está actualizado pero no se aplica, Sí, pero está desactualizado, No, pero se encuentra en diseño, No.</t>
       </text>
     </comment>
     <comment ref="I3" authorId="0" shapeId="0">
       <text>
         <t>¿Cuenta con Normativa Convivencial?
-Qué se espera: texto
-Máximo 38 caracteres.
-Elegir de la lista "Cuenta con Normativa Convivencial".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, es una herramienta de gestión, Sí, está actualizada pero no se aplica, Sí, pero está desactualizada, No, pero se encuentra en diseño, No.</t>
       </text>
     </comment>
     <comment ref="J3" authorId="0" shapeId="0">
       <text>
         <t>Cantidad de agentes: equipo técnico y profesional (incluye cuidadores)
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.
+Aviso: Entre 10 y 200.
+Entre 0 y 5000.</t>
       </text>
     </comment>
     <comment ref="K3" authorId="0" shapeId="0">
       <text>
         <t>Cantidad agentes de salud
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.
+Aviso: Entre 0 y 200.
+Entre 0 y 5000.</t>
       </text>
     </comment>
     <comment ref="L3" authorId="0" shapeId="0">
       <text>
         <t>Cantidad de personal: administrativo, limpieza, cocina y mantenimiento
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.
+Aviso: Entre 10 y 200.
+Entre 0 y 5000.</t>
       </text>
     </comment>
     <comment ref="M3" authorId="0" shapeId="0">
       <text>
         <t>Cantidad de personal seguridad
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.
+Aviso: Entre 0 y 200.
+Entre 0 y 5000.</t>
       </text>
     </comment>
     <comment ref="N3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con protocolos de ingreso
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="O3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con protocolo de requisa
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="P3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con protocolo de denuncias por malos tratos
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="Q3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con protocolos de actuación ante conflictos entre pares
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="R3" authorId="0" shapeId="0">
       <text>
         <t>Protocolo de abordaje del suicidio
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="S3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con protocolo de sanciones
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="T3" authorId="0" shapeId="0">
       <text>
         <t>Cantidad de horas semanales destinadas al contacto presencial, afectivo/familiar
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.
+Entre 0 y 168.</t>
       </text>
     </comment>
     <comment ref="U3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con espacios para visitas socioafectivas
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="V3" authorId="0" shapeId="0">
       <text>
         <t>Cumple con los niveles de obligatoriedad de educación primaria
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Cumple con los niveles de obligatoriedad de educación primaria".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, con convenio ME, Sí, sin convenio ME, No.</t>
       </text>
     </comment>
     <comment ref="W3" authorId="0" shapeId="0">
       <text>
         <t>Cantidad de horas semanales dedicadas a la educación primaria
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.
+Entre 0 y 168.</t>
       </text>
     </comment>
     <comment ref="X3" authorId="0" shapeId="0">
       <text>
         <t>Cumple con los niveles de obligatoriedad de educación secundaria
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Cumple con los niveles de obligatoriedad de educación primaria".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, con convenio ME, Sí, sin convenio ME, No.</t>
       </text>
     </comment>
     <comment ref="Y3" authorId="0" shapeId="0">
       <text>
         <t>Cantidad de horas semanales dedicadas a la educación secundaria
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.
+Entre 0 y 168.</t>
       </text>
     </comment>
     <comment ref="Z3" authorId="0" shapeId="0">
       <text>
         <t>Tiene aulas destinadas a la educación obligatoria
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="AA3" authorId="0" shapeId="0">
       <text>
         <t>Cantidad de horas semanales dedicadas a la formación profesional
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.
+Entre 0 y 168.</t>
       </text>
     </comment>
     <comment ref="AB3" authorId="0" shapeId="0">
       <text>
         <t>Cantidad de horas semanales dedicadas a talleres deportivos y culturales
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.
+Entre 0 y 168.</t>
       </text>
     </comment>
     <comment ref="AC3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con espacio para talleres
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="AD3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con asesoramiento técnico jurídico
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="AE3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con patio abierto
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="AF3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con patio techado
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="AG3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con celdas secas
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="AH3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con celdas humedas
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="AI3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con mobiliario en las celdas
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="AJ3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con colchones ignífugos
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
   </commentList>
@@ -500,304 +479,292 @@
 <file path=xl/comments/comment2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>RUNAC</author>
+    <author>MIR</author>
   </authors>
   <commentList>
     <comment ref="A3" authorId="0" shapeId="0">
       <text>
         <t>Nombre del dispositvo
-Qué se espera: texto
-Máximo 120 caracteres.
-Campo obligatorio.</t>
+Obligatorio
+Qué va: Texto, hasta 120 caracteres.</t>
       </text>
     </comment>
     <comment ref="B3" authorId="0" shapeId="0">
       <text>
         <t>Dependencia institucional
-Qué se espera: texto
-Máximo 255 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 255 caracteres.</t>
       </text>
     </comment>
     <comment ref="C3" authorId="0" shapeId="0">
       <text>
         <t>Localidad
-Qué se espera: texto
-Máximo 120 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 120 caracteres.</t>
       </text>
     </comment>
     <comment ref="D3" authorId="0" shapeId="0">
       <text>
         <t>Dirección
-Qué se espera: texto
-Máximo 255 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 255 caracteres.</t>
       </text>
     </comment>
     <comment ref="E3" authorId="0" shapeId="0">
       <text>
         <t>Teléfono
-Qué se espera: texto
-Máximo 50 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 50 caracteres.</t>
       </text>
     </comment>
     <comment ref="F3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con Proyecto Institucional
-Qué se espera: texto
-Máximo 38 caracteres.
-Elegir de la lista "Cuenta con Proyecto Institucional".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, es una herramienta de gestión, Sí, está actualizado pero no se aplica, Sí, pero está desactualizado, No, pero se encuentra en diseño, No.</t>
       </text>
     </comment>
     <comment ref="G3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con Normativa Convivencial
-Qué se espera: texto
-Máximo 38 caracteres.
-Elegir de la lista "Cuenta con Normativa Convivencial".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, es una herramienta de gestión, Sí, está actualizada pero no se aplica, Sí, pero está desactualizada, No, pero se encuentra en diseño, No.</t>
       </text>
     </comment>
     <comment ref="H3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con protocolos de ingreso
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="I3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con protocolo de requisa
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="J3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con protocolo de denuncias por malos tratos
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="K3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con protocolos de actuación ante conflictos entre pares
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="L3" authorId="0" shapeId="0">
       <text>
         <t>Protocolo de abordaje del suicidio
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="M3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con protocolo de sanciones
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="N3" authorId="0" shapeId="0">
       <text>
         <t>Capacidad de alojamiento mujeres (plazas disponibles)
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.</t>
       </text>
     </comment>
     <comment ref="O3" authorId="0" shapeId="0">
       <text>
         <t>Capacidad de alojamiento varones (plazas disponibles)
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.</t>
       </text>
     </comment>
     <comment ref="P3" authorId="0" shapeId="0">
       <text>
         <t>Cantidad de agentes: equipo técnico y profesional (incluye cuidadores)
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.
+Aviso: Entre 0 y 200.
+Entre 0 y 5000.</t>
       </text>
     </comment>
     <comment ref="Q3" authorId="0" shapeId="0">
       <text>
         <t>Cantidad agentes de salud
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.
+Aviso: Entre 0 y 200.
+Entre 0 y 5000.</t>
       </text>
     </comment>
     <comment ref="R3" authorId="0" shapeId="0">
       <text>
         <t>Cantidad de personal: administrativo, limpieza, cocina y mantenimiento
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.
+Aviso: Entre 0 y 200.
+Entre 0 y 5000.</t>
       </text>
     </comment>
     <comment ref="S3" authorId="0" shapeId="0">
       <text>
         <t>Cantidad de personal seguridad
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.
+Aviso: Entre 0 y 200.
+Entre 0 y 5000.</t>
       </text>
     </comment>
     <comment ref="T3" authorId="0" shapeId="0">
       <text>
         <t>Cantidad de horas semanales destinadas al contacto presencial, afectivo/familiar
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.
+Entre 0 y 168.</t>
       </text>
     </comment>
     <comment ref="U3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con espacios para visitas socioafectivas
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="V3" authorId="0" shapeId="0">
       <text>
         <t>Cumple con los niveles de obligatoriedad de educación primaria
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Cumple con los niveles de obligatoriedad de educación primaria".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, con convenio ME, Sí, sin convenio ME, No.</t>
       </text>
     </comment>
     <comment ref="W3" authorId="0" shapeId="0">
       <text>
         <t>Cantidad de horas semanales dedicadas a la educación primaria
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.
+Entre 0 y 168.</t>
       </text>
     </comment>
     <comment ref="X3" authorId="0" shapeId="0">
       <text>
         <t>Cumple con los niveles de obligatoriedad de educación secundaria
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Cumple con los niveles de obligatoriedad de educación primaria".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, con convenio ME, Sí, sin convenio ME, No.</t>
       </text>
     </comment>
     <comment ref="Y3" authorId="0" shapeId="0">
       <text>
         <t>Cantidad de horas semanales dedicadas a la educación secundaria
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.
+Entre 0 y 168.</t>
       </text>
     </comment>
     <comment ref="Z3" authorId="0" shapeId="0">
       <text>
         <t>Tiene aulas destinadas a la educación obligatoria
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="AA3" authorId="0" shapeId="0">
       <text>
         <t>Cantidad de horas semanales dedicadas a la formación profesional
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.
+Entre 0 y 168.</t>
       </text>
     </comment>
     <comment ref="AB3" authorId="0" shapeId="0">
       <text>
         <t>Cantidad de horas semanales dedicadas a talleres deportivos y culturales
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.
+Entre 0 y 168.</t>
       </text>
     </comment>
     <comment ref="AC3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con espacio para talleres
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="AD3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con asesoramiento técnico jurídico
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="AE3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con patio abierto
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="AF3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con patio techado
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="AG3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con celdas secas
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="AH3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con celdas humedas
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="AI3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con mobiliario en las celdas
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="AJ3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con colchones ignífugos
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
   </commentList>
@@ -807,89 +774,82 @@
 <file path=xl/comments/comment3.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>RUNAC</author>
+    <author>MIR</author>
   </authors>
   <commentList>
     <comment ref="A3" authorId="0" shapeId="0">
       <text>
         <t>Nombre del dispositvo
-Qué se espera: texto
-Máximo 120 caracteres.
-Campo obligatorio.</t>
+Obligatorio
+Qué va: Texto, hasta 120 caracteres.</t>
       </text>
     </comment>
     <comment ref="B3" authorId="0" shapeId="0">
       <text>
         <t>Dependencia institucional
-Qué se espera: texto
-Máximo 255 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 255 caracteres.</t>
       </text>
     </comment>
     <comment ref="C3" authorId="0" shapeId="0">
       <text>
         <t>Localidad
-Qué se espera: texto
-Máximo 120 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 120 caracteres.</t>
       </text>
     </comment>
     <comment ref="D3" authorId="0" shapeId="0">
       <text>
         <t>Dirección
-Qué se espera: texto
-Máximo 255 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 255 caracteres.</t>
       </text>
     </comment>
     <comment ref="E3" authorId="0" shapeId="0">
       <text>
         <t>Teléfono
-Qué se espera: texto
-Máximo 50 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 50 caracteres.</t>
       </text>
     </comment>
     <comment ref="F3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con Proyecto Institucional
-Qué se espera: texto
-Máximo 38 caracteres.
-Elegir de la lista "Cuenta con Proyecto Institucional".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, es una herramienta de gestión, Sí, está actualizado pero no se aplica, Sí, pero está desactualizado, No, pero se encuentra en diseño, No.</t>
       </text>
     </comment>
     <comment ref="G3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con espacio de grupalidad
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="H3" authorId="0" shapeId="0">
       <text>
         <t>Cantidad de agentes: equipo técnico y profesional (incluye cuidadores)
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.
+Aviso: Entre 0 y 200.
+Entre 0 y 5000.</t>
       </text>
     </comment>
     <comment ref="I3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con asesoramiento técnico jurídico
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="J3" authorId="0" shapeId="0">
       <text>
         <t>Jurisdicciones dentro de la provincia en las que el dispositivo tiene alcance
-Qué se espera: texto
-Máximo 120 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 120 caracteres.</t>
       </text>
     </comment>
   </commentList>
@@ -899,230 +859,218 @@
 <file path=xl/comments/comment4.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>RUNAC</author>
+    <author>MIR</author>
   </authors>
   <commentList>
     <comment ref="A3" authorId="0" shapeId="0">
       <text>
         <t>Nombre del dispositvo
-Qué se espera: texto
-Máximo 120 caracteres.
-Campo obligatorio.</t>
+Obligatorio
+Qué va: Texto, hasta 120 caracteres.</t>
       </text>
     </comment>
     <comment ref="B3" authorId="0" shapeId="0">
       <text>
         <t>Dependencia institucional
-Qué se espera: texto
-Máximo 255 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 255 caracteres.</t>
       </text>
     </comment>
     <comment ref="C3" authorId="0" shapeId="0">
       <text>
         <t>Localidad
-Qué se espera: texto
-Máximo 120 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 120 caracteres.</t>
       </text>
     </comment>
     <comment ref="D3" authorId="0" shapeId="0">
       <text>
         <t>Dirección
-Qué se espera: texto
-Máximo 255 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 255 caracteres.</t>
       </text>
     </comment>
     <comment ref="E3" authorId="0" shapeId="0">
       <text>
         <t>Teléfono
-Qué se espera: texto
-Máximo 50 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 50 caracteres.</t>
       </text>
     </comment>
     <comment ref="F3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con Proyecto Institucional
-Qué se espera: texto
-Máximo 38 caracteres.
-Elegir de la lista "Cuenta con Proyecto Institucional".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, es una herramienta de gestión, Sí, está actualizado pero no se aplica, Sí, pero está desactualizado, No, pero se encuentra en diseño, No.</t>
       </text>
     </comment>
     <comment ref="G3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con resolución de creación
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="H3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con Normativa Convivencial
-Qué se espera: texto
-Máximo 38 caracteres.
-Elegir de la lista "Cuenta con Normativa Convivencial".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, es una herramienta de gestión, Sí, está actualizada pero no se aplica, Sí, pero está desactualizada, No, pero se encuentra en diseño, No.</t>
       </text>
     </comment>
     <comment ref="I3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con protocolos de articulación interministerial. Con qué áreas
-Qué se espera: texto
-Máximo 34 caracteres.
-Elegir de la lista "Cuenta con protocolos de articulación interministerial. Con qué áreas".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, con áreas de salud y seguridad, Sí, con áreas de seguridad, Sí, con áreas de salud, No.</t>
       </text>
     </comment>
     <comment ref="J3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con protocolos de ingreso
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="K3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con protocolo de requisa
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="L3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con protocolo de denuncias por malos tratos
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="M3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con protocolos de actuación ante conflictos entre pares
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="N3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con protocolo de abordaje del suicidio
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="O3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con protocolo de sanciones
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="P3" authorId="0" shapeId="0">
       <text>
         <t>Capacidad de alojamiento mujeres (plazas disponibles)
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.</t>
       </text>
     </comment>
     <comment ref="Q3" authorId="0" shapeId="0">
       <text>
         <t>Capacidad de alojamiento varones (plazas disponibles)
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.</t>
       </text>
     </comment>
     <comment ref="R3" authorId="0" shapeId="0">
       <text>
         <t>Cantidad de agentes: equipo técnico y profesional (incluye cuidadores)
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.
+Aviso: Entre 0 y 200.
+Entre 0 y 5000.</t>
       </text>
     </comment>
     <comment ref="S3" authorId="0" shapeId="0">
       <text>
         <t>Cantidad agentes de salud
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.
+Aviso: Entre 0 y 200.
+Entre 0 y 5000.</t>
       </text>
     </comment>
     <comment ref="T3" authorId="0" shapeId="0">
       <text>
         <t>Cantidad de personal: administrativo, limpieza, cocina y mantenimiento
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.
+Aviso: Entre 0 y 200.
+Entre 0 y 5000.</t>
       </text>
     </comment>
     <comment ref="U3" authorId="0" shapeId="0">
       <text>
         <t>Cantidad de personal seguridad
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.
+Aviso: Entre 0 y 200.
+Entre 0 y 5000.</t>
       </text>
     </comment>
     <comment ref="V3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con celdas secas
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="W3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con celdas humedas
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="X3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con mobiliario en las celdas
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="Y3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con colchones ignífugos
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="Z3" authorId="0" shapeId="0">
       <text>
         <t>Jurisdicciones dentro de la provincia en las que tiene alcancce territorial el dispositivo
-Qué se espera: texto
-Máximo 120 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 120 caracteres.</t>
       </text>
     </comment>
     <comment ref="AA3" authorId="0" shapeId="0">
       <text>
         <t>Tiempo máximo de permanencia dentro del dispositivo (en horas)
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.</t>
       </text>
     </comment>
   </commentList>
@@ -1132,80 +1080,75 @@
 <file path=xl/comments/comment5.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
-    <author>RUNAC</author>
+    <author>MIR</author>
   </authors>
   <commentList>
     <comment ref="A3" authorId="0" shapeId="0">
       <text>
         <t>Nombre del dispositvo
-Qué se espera: texto
-Máximo 120 caracteres.
-Campo obligatorio.</t>
+Obligatorio
+Qué va: Texto, hasta 120 caracteres.</t>
       </text>
     </comment>
     <comment ref="B3" authorId="0" shapeId="0">
       <text>
         <t>Dependencia institucional
-Qué se espera: texto
-Máximo 255 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 255 caracteres.</t>
       </text>
     </comment>
     <comment ref="C3" authorId="0" shapeId="0">
       <text>
         <t>Teléfono
-Qué se espera: texto
-Máximo 50 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 50 caracteres.</t>
       </text>
     </comment>
     <comment ref="D3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con resolución de creación
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="E3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con protocolos de articulación interministerial. Con qué áreas
-Qué se espera: texto
-Máximo 34 caracteres.
-Elegir de la lista "Cuenta con protocolos de articulación interministerial. Con qué áreas".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, con áreas de salud y seguridad, Sí, con áreas de seguridad, Sí, con áreas de salud, No.</t>
       </text>
     </comment>
     <comment ref="F3" authorId="0" shapeId="0">
       <text>
         <t>Cuenta con protocolo de denuncias por malos tratos
-Qué se espera: texto
-Máximo 20 caracteres.
-Elegir de la lista "Sí / No / Sin datos".
-No es obligatorio.</t>
+Opcional
+Qué va: Una opción de la lista.
+Valores: Sí, No, Sin datos.</t>
       </text>
     </comment>
     <comment ref="G3" authorId="0" shapeId="0">
       <text>
         <t>Cantidad de agentes: equipo técnico y profesional (incluye cuidadores)
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.
+Aviso: Entre 0 y 200.
+Entre 0 y 5000.</t>
       </text>
     </comment>
     <comment ref="H3" authorId="0" shapeId="0">
       <text>
         <t>Jurisdicciones dentro de la provincia en las que tiene alcancce territorial el dispositivo
-Qué se espera: texto
-Máximo 120 caracteres.
-No es obligatorio.</t>
+Opcional
+Qué va: Texto, hasta 120 caracteres.</t>
       </text>
     </comment>
     <comment ref="I3" authorId="0" shapeId="0">
       <text>
         <t>Tiempo máximo de permanencia dentro del dispositivo (en horas)
-Qué se espera: un número entero
-No es obligatorio.</t>
+Opcional
+Qué va: Número entero.</t>
       </text>
     </comment>
   </commentList>
@@ -1781,10 +1724,10 @@
         <v>14</v>
       </c>
       <c r="L4" s="4" t="n">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="M4" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -1798,7 +1741,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -1808,20 +1751,20 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="T4" s="4" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1830,7 +1773,7 @@
         </is>
       </c>
       <c r="W4" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -1838,27 +1781,27 @@
         </is>
       </c>
       <c r="Y4" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AA4" s="4" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="AB4" s="4" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
@@ -1868,12 +1811,12 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
@@ -1888,7 +1831,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -1900,116 +1843,116 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ministerio de Desarrollo Social</t>
+          <t>Subsecretaría de Niñez y Adolescencia</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>General San Martín</t>
+          <t>Barranqueras</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>San Martín 859</t>
+          <t>San Martín 3212</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>11-4489-2584</t>
+          <t>11-4199-6881</t>
         </is>
       </c>
       <c r="F5" s="4" t="n">
         <v>30</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí, pero está desactualizado</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>Sí, pero está desactualizada</t>
+          <t>Sí, es una herramienta de gestión</t>
         </is>
       </c>
       <c r="J5" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="K5" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="L5" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="M5" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="T5" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Sí, con convenio ME</t>
+        </is>
+      </c>
+      <c r="W5" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Sí, con convenio ME</t>
+        </is>
+      </c>
+      <c r="Y5" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="K5" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="L5" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="M5" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="T5" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W5" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y5" s="4" t="n">
-        <v>3</v>
-      </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AA5" s="4" t="n">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="AB5" s="4" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
@@ -2255,90 +2198,90 @@
         </is>
       </c>
       <c r="J7" s="4" t="n">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="L7" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="M7" s="4" t="n">
         <v>19</v>
       </c>
-      <c r="M7" s="4" t="n">
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T7" s="4" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Sí, con convenio ME</t>
+        </is>
+      </c>
+      <c r="W7" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y7" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="AA7" s="4" t="n">
         <v>14</v>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="T7" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Sí, con convenio ME</t>
-        </is>
-      </c>
-      <c r="W7" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>Sí, con convenio ME</t>
-        </is>
-      </c>
-      <c r="Y7" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AA7" s="4" t="n">
-        <v>22</v>
-      </c>
       <c r="AB7" s="4" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
@@ -2348,39 +2291,39 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Hogar Nuestra Señora</t>
+          <t>Hogar Los Álamos</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Secretaría de Niñez, Adolescencia y Familia</t>
+          <t>Servicio de Protección de Derechos</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -2421,14 +2364,14 @@
         <v>14</v>
       </c>
       <c r="L8" s="4" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="M8" s="4" t="n">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -2438,39 +2381,39 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="T8" s="4" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí, sin convenio ME</t>
         </is>
       </c>
       <c r="W8" s="4" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="X8" t="inlineStr">
         <is>
@@ -2478,27 +2421,27 @@
         </is>
       </c>
       <c r="Y8" s="4" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AA8" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AB8" s="4" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -2508,17 +2451,17 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
@@ -2528,7 +2471,7 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
@@ -2540,117 +2483,117 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Secretaría de Niñez, Adolescencia y Familia</t>
+          <t>Subsecretaría de Niñez y Adolescencia</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>General San Martín</t>
+          <t>Charata</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Güemes 2619</t>
+          <t>Belgrano 574</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>11-4345-1949</t>
+          <t>11-4346-2290</t>
         </is>
       </c>
       <c r="F9" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="G9" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>No, pero se encuentra en diseño</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Sí, es una herramienta de gestión</t>
+        </is>
+      </c>
+      <c r="J9" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="K9" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="L9" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="M9" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="T9" s="4" t="n">
+        <v>17</v>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Sí, sin convenio ME</t>
+        </is>
+      </c>
+      <c r="W9" s="4" t="n">
+        <v>7</v>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y9" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="AA9" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="G9" s="4" t="n">
-        <v>44</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Sí, es una herramienta de gestión</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>Sí, es una herramienta de gestión</t>
-        </is>
-      </c>
-      <c r="J9" s="4" t="n">
-        <v>24</v>
-      </c>
-      <c r="K9" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="L9" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="M9" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="T9" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W9" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>Sí, sin convenio ME</t>
-        </is>
-      </c>
-      <c r="Y9" s="4" t="n">
+      <c r="AB9" s="4" t="n">
         <v>7</v>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="AA9" s="4" t="n">
-        <v>25</v>
-      </c>
-      <c r="AB9" s="4" t="n">
-        <v>24</v>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
           <t>Sin datos</t>
@@ -2658,37 +2601,37 @@
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
     </row>
@@ -2700,33 +2643,33 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Convenio con organización civil</t>
+          <t>Secretaría de Niñez, Adolescencia y Familia</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Quitilipi</t>
+          <t>Villa Ángela</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>San Martín 2130</t>
+          <t>Belgrano 624</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>11-4330-2049</t>
+          <t>11-4446-1344</t>
         </is>
       </c>
       <c r="F10" s="4" t="n">
-        <v>29</v>
+        <v>45</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí, está actualizado pero no se aplica</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -2735,16 +2678,16 @@
         </is>
       </c>
       <c r="J10" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K10" s="4" t="n">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="L10" s="4" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="M10" s="4" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -2753,12 +2696,12 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -2768,7 +2711,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -2777,28 +2720,28 @@
         </is>
       </c>
       <c r="T10" s="4" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>Sí, con convenio ME</t>
+          <t>Sí, sin convenio ME</t>
         </is>
       </c>
       <c r="W10" s="4" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>Sí, con convenio ME</t>
+          <t>Sí, sin convenio ME</t>
         </is>
       </c>
       <c r="Y10" s="4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
@@ -2806,10 +2749,10 @@
         </is>
       </c>
       <c r="AA10" s="4" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="AB10" s="4" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
@@ -2818,22 +2761,22 @@
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
@@ -2848,41 +2791,41 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Programa de Acompañamiento Sur</t>
+          <t>Hogar Los Álamos</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ministerio de Desarrollo Social</t>
+          <t>Servicio de Protección de Derechos</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Barranqueras</t>
+          <t>Las Breñas</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>San Martín 3631</t>
+          <t>Rivadavia 3569</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>11-4462-7939</t>
+          <t>11-4520-8651</t>
         </is>
       </c>
       <c r="F11" s="4" t="n">
-        <v>34</v>
+        <v>54</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>37</v>
+        <v>11</v>
       </c>
       <c r="H11" t="inlineStr">
         <is>
@@ -2895,16 +2838,16 @@
         </is>
       </c>
       <c r="J11" s="4" t="n">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="K11" s="4" t="n">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="L11" s="4" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="M11" s="4" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -2923,53 +2866,53 @@
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="T11" s="4" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>Sí, sin convenio ME</t>
+        </is>
+      </c>
+      <c r="W11" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
           <t>Sí, con convenio ME</t>
         </is>
       </c>
-      <c r="W11" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>Sí, sin convenio ME</t>
-        </is>
-      </c>
       <c r="Y11" s="4" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AA11" s="4" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AB11" s="4" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
@@ -2978,7 +2921,7 @@
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
@@ -2988,7 +2931,7 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -3008,7 +2951,7 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3025,12 +2968,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Quitilipi</t>
+          <t>Villa Ángela</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Belgrano 3385</t>
+          <t>Güemes 3385</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -3375,13 +3318,13 @@
         </is>
       </c>
       <c r="J14" s="4" t="n">
-        <v>5</v>
+        <v>39</v>
       </c>
       <c r="K14" s="4" t="n">
         <v>12</v>
       </c>
       <c r="L14" s="4" t="n">
-        <v>3</v>
+        <v>38</v>
       </c>
       <c r="M14" s="4" t="n">
         <v>8</v>
@@ -3535,81 +3478,81 @@
         </is>
       </c>
       <c r="J15" s="4" t="n">
+        <v>30</v>
+      </c>
+      <c r="K15" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="L15" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="M15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="T15" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W15" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y15" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AA15" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="K15" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="L15" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="M15" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="T15" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Sí, sin convenio ME</t>
-        </is>
-      </c>
-      <c r="W15" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y15" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="AA15" s="4" t="n">
-        <v>1</v>
-      </c>
       <c r="AB15" s="4" t="n">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
@@ -3628,27 +3571,27 @@
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3660,51 +3603,51 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Municipalidad de Rawson</t>
+          <t>Secretaría de Niñez, Adolescencia y Familia</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Presidencia Roque Sáenz Peña</t>
+          <t>Charata</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>San Martín 2625</t>
+          <t>Rivadavia 426</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>11-4473-1653</t>
+          <t>11-4466-4441</t>
         </is>
       </c>
       <c r="F16" s="4" t="n">
-        <v>30</v>
+        <v>51</v>
       </c>
       <c r="G16" s="4" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Sí, está actualizado pero no se aplica</t>
+          <t>Sí, es una herramienta de gestión</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Sí, es una herramienta de gestión</t>
+          <t>Sí, pero está desactualizada</t>
         </is>
       </c>
       <c r="J16" s="4" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="K16" s="4" t="n">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="L16" s="4" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="M16" s="4" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -3713,7 +3656,7 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -3733,11 +3676,11 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="T16" s="4" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="U16" t="inlineStr">
         <is>
@@ -3746,11 +3689,11 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>Sí, con convenio ME</t>
+          <t>No</t>
         </is>
       </c>
       <c r="W16" s="4" t="n">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="X16" t="inlineStr">
         <is>
@@ -3758,7 +3701,7 @@
         </is>
       </c>
       <c r="Y16" s="4" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
@@ -3766,44 +3709,44 @@
         </is>
       </c>
       <c r="AA16" s="4" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="AB16" s="4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
@@ -3815,22 +3758,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Residencia El Ceibo</t>
+          <t>Programa de Acompañamiento Sur</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Municipalidad de Rawson</t>
+          <t>Subsecretaría de Niñez y Adolescencia</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>General San Martín</t>
+          <t>Charata</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Rivadavia 1964</t>
+          <t>Güemes 1964</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -3855,7 +3798,7 @@
         </is>
       </c>
       <c r="J17" s="4" t="n">
-        <v>9</v>
+        <v>37</v>
       </c>
       <c r="K17" s="4" t="n">
         <v>3</v>
@@ -4021,7 +3964,7 @@
         <v>14</v>
       </c>
       <c r="L18" s="4" t="n">
-        <v>3</v>
+        <v>40</v>
       </c>
       <c r="M18" s="4" t="n">
         <v>22</v>
@@ -4655,7 +4598,7 @@
         </is>
       </c>
       <c r="J22" s="4" t="n">
-        <v>7</v>
+        <v>36</v>
       </c>
       <c r="K22" s="4" t="n">
         <v>14</v>
@@ -4815,7 +4758,7 @@
         </is>
       </c>
       <c r="J23" s="4" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="K23" s="4" t="n">
         <v>13</v>
@@ -4975,90 +4918,90 @@
         </is>
       </c>
       <c r="J24" s="4" t="n">
-        <v>1</v>
+        <v>29</v>
       </c>
       <c r="K24" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="L24" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="M24" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="T24" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Sí, con convenio ME</t>
+        </is>
+      </c>
+      <c r="W24" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="L24" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="M24" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="R24" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="T24" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>Sí, sin convenio ME</t>
-        </is>
-      </c>
-      <c r="W24" s="4" t="n">
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y24" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="AA24" s="4" t="n">
+        <v>4</v>
+      </c>
+      <c r="AB24" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="X24" t="inlineStr">
-        <is>
-          <t>Sí, sin convenio ME</t>
-        </is>
-      </c>
-      <c r="Y24" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="AA24" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="AB24" s="4" t="n">
-        <v>24</v>
-      </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AD24" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AE24" t="inlineStr">
@@ -5068,7 +5011,7 @@
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AG24" t="inlineStr">
@@ -5078,44 +5021,44 @@
       </c>
       <c r="AH24" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AI24" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AJ24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Hogar Nuestra Señora</t>
+          <t>Programa de Acompañamiento Sur</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Servicio de Protección de Derechos</t>
+          <t>Municipalidad de Rawson</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Las Breñas</t>
+          <t>Villa Ángela</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Mitre 1724</t>
+          <t>San Martín 4950</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>11-4177-4978</t>
+          <t>11-4807-4978</t>
         </is>
       </c>
       <c r="F25" s="4" t="n">
@@ -5135,40 +5078,40 @@
         </is>
       </c>
       <c r="J25" s="4" t="n">
-        <v>4</v>
+        <v>35</v>
       </c>
       <c r="K25" s="4" t="n">
         <v>19</v>
       </c>
       <c r="L25" s="4" t="n">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="M25" s="4" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="S25" t="inlineStr">
@@ -5177,63 +5120,63 @@
         </is>
       </c>
       <c r="T25" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Sí, sin convenio ME</t>
+        </is>
+      </c>
+      <c r="W25" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="X25" t="inlineStr">
+        <is>
+          <t>Sí, con convenio ME</t>
+        </is>
+      </c>
+      <c r="Y25" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA25" s="4" t="n">
         <v>21</v>
       </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>Sí, con convenio ME</t>
-        </is>
-      </c>
-      <c r="W25" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="X25" t="inlineStr">
-        <is>
-          <t>Sí, sin convenio ME</t>
-        </is>
-      </c>
-      <c r="Y25" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA25" s="4" t="n">
-        <v>12</v>
-      </c>
       <c r="AB25" s="4" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AD25" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AG25" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AH25" t="inlineStr">
@@ -5248,14 +5191,14 @@
       </c>
       <c r="AJ25" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Centro Municipal Norte</t>
+          <t>Hogar Nuestra Señora</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5455,81 +5398,81 @@
         </is>
       </c>
       <c r="J27" s="4" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="K27" s="4" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L27" s="4" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="M27" s="4" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="T27" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Sí, sin convenio ME</t>
+        </is>
+      </c>
+      <c r="W27" s="4" t="n">
+        <v>14</v>
+      </c>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y27" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA27" s="4" t="n">
         <v>12</v>
       </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W27" s="4" t="n">
-        <v>17</v>
-      </c>
-      <c r="X27" t="inlineStr">
-        <is>
-          <t>Sí, sin convenio ME</t>
-        </is>
-      </c>
-      <c r="Y27" s="4" t="n">
-        <v>14</v>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="AA27" s="4" t="n">
-        <v>18</v>
-      </c>
       <c r="AB27" s="4" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
@@ -5538,7 +5481,7 @@
       </c>
       <c r="AD27" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AE27" t="inlineStr">
@@ -5553,17 +5496,17 @@
       </c>
       <c r="AG27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AH27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AI27" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AJ27" t="inlineStr">
@@ -5575,70 +5518,70 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Residencia El Ceibo</t>
+          <t>Centro Municipal Norte</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Subsecretaría de Niñez y Adolescencia</t>
+          <t>Secretaría de Niñez, Adolescencia y Familia</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Barranqueras</t>
+          <t>Presidencia Roque Sáenz Peña</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Alberdi 4489</t>
+          <t>Belgrano 1872</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>11-4880-4033</t>
+          <t>11-4856-8933</t>
         </is>
       </c>
       <c r="F28" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="G28" s="4" t="n">
+        <v>54</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="n">
         <v>20</v>
       </c>
-      <c r="G28" s="4" t="n">
-        <v>21</v>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>No, pero se encuentra en diseño</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Sí, pero está desactualizada</t>
-        </is>
-      </c>
-      <c r="J28" s="4" t="n">
-        <v>24</v>
-      </c>
       <c r="K28" s="4" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="L28" s="4" t="n">
-        <v>25</v>
+        <v>36</v>
       </c>
       <c r="M28" s="4" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
@@ -5657,39 +5600,39 @@
         </is>
       </c>
       <c r="T28" s="4" t="n">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="U28" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="V28" t="inlineStr">
         <is>
-          <t>Sí, sin convenio ME</t>
+          <t>Sí, con convenio ME</t>
         </is>
       </c>
       <c r="W28" s="4" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí, con convenio ME</t>
         </is>
       </c>
       <c r="Y28" s="4" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AA28" s="4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB28" s="4" t="n">
-        <v>2</v>
+        <v>23</v>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
@@ -5708,7 +5651,7 @@
       </c>
       <c r="AF28" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AG28" t="inlineStr">
@@ -5728,45 +5671,45 @@
       </c>
       <c r="AJ28" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hogar Los Álamos</t>
+          <t>Programa de Acompañamiento Sur</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Convenio con organización civil</t>
+          <t>Municipalidad de Rawson</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Charata</t>
+          <t>General San Martín</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Mitre 4021</t>
+          <t>Belgrano 520</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>11-4551-6582</t>
+          <t>11-4358-8827</t>
         </is>
       </c>
       <c r="F29" s="4" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G29" s="4" t="n">
-        <v>11</v>
+        <v>60</v>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Sí, pero está desactualizado</t>
+          <t>Sí, es una herramienta de gestión</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -5775,70 +5718,70 @@
         </is>
       </c>
       <c r="J29" s="4" t="n">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="K29" s="4" t="n">
         <v>3</v>
       </c>
       <c r="L29" s="4" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="M29" s="4" t="n">
-        <v>16</v>
+        <v>21</v>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="T29" s="4" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="U29" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="V29" t="inlineStr">
         <is>
+          <t>Sí, con convenio ME</t>
+        </is>
+      </c>
+      <c r="W29" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="X29" t="inlineStr">
+        <is>
           <t>Sí, sin convenio ME</t>
         </is>
       </c>
-      <c r="W29" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="X29" t="inlineStr">
-        <is>
-          <t>Sí, con convenio ME</t>
-        </is>
-      </c>
       <c r="Y29" s="4" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
@@ -5846,10 +5789,10 @@
         </is>
       </c>
       <c r="AA29" s="4" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AB29" s="4" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
@@ -5858,27 +5801,27 @@
       </c>
       <c r="AD29" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AE29" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AF29" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AG29" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AH29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AI29" t="inlineStr">
@@ -5895,7 +5838,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Centro Municipal Norte</t>
+          <t>Hogar Nuestra Señora</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -5905,46 +5848,46 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Las Breñas</t>
+          <t>Resistencia</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Rivadavia 4758</t>
+          <t>Sarmiento 912</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>11-4735-1986</t>
+          <t>11-4881-4404</t>
         </is>
       </c>
       <c r="F30" s="4" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G30" s="4" t="n">
-        <v>55</v>
+        <v>21</v>
       </c>
       <c r="H30" t="inlineStr">
         <is>
+          <t>Sí, pero está desactualizado</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
           <t>Sí, es una herramienta de gestión</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Sí, está actualizada pero no se aplica</t>
-        </is>
-      </c>
       <c r="J30" s="4" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="K30" s="4" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L30" s="4" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="M30" s="4" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
       <c r="N30" t="inlineStr">
         <is>
@@ -5958,12 +5901,12 @@
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -5973,44 +5916,44 @@
       </c>
       <c r="S30" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="T30" s="4" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="U30" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="V30" t="inlineStr">
         <is>
+          <t>Sí, con convenio ME</t>
+        </is>
+      </c>
+      <c r="W30" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="X30" t="inlineStr">
+        <is>
           <t>Sí, sin convenio ME</t>
         </is>
       </c>
-      <c r="W30" s="4" t="n">
+      <c r="Y30" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA30" s="4" t="n">
+        <v>23</v>
+      </c>
+      <c r="AB30" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="X30" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Y30" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA30" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="AB30" s="4" t="n">
-        <v>2</v>
-      </c>
       <c r="AC30" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -6018,12 +5961,12 @@
       </c>
       <c r="AD30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AE30" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AF30" t="inlineStr">
@@ -6038,29 +5981,29 @@
       </c>
       <c r="AH30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AJ30" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Residencia El Ceibo</t>
+          <t>Programa de Acompañamiento Sur</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Subsecretaría de Niñez y Adolescencia</t>
+          <t>Secretaría de Niñez, Adolescencia y Familia</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -6070,60 +6013,60 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Mitre 1040</t>
+          <t>Alberdi 1320</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>11-4657-4683</t>
+          <t>11-4372-3330</t>
         </is>
       </c>
       <c r="F31" s="4" t="n">
-        <v>49</v>
+        <v>12</v>
       </c>
       <c r="G31" s="4" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Sí, pero está desactualizado</t>
+          <t>Sí, está actualizado pero no se aplica</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Sí, está actualizada pero no se aplica</t>
+          <t>Sí, pero está desactualizada</t>
         </is>
       </c>
       <c r="J31" s="4" t="n">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="K31" s="4" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="L31" s="4" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="M31" s="4" t="n">
         <v>10</v>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -6133,43 +6076,43 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="T31" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W31" s="4" t="n">
+        <v>18</v>
+      </c>
+      <c r="X31" t="inlineStr">
+        <is>
+          <t>Sí, sin convenio ME</t>
+        </is>
+      </c>
+      <c r="Y31" s="4" t="n">
         <v>15</v>
       </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>Sí, sin convenio ME</t>
-        </is>
-      </c>
-      <c r="W31" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="X31" t="inlineStr">
-        <is>
-          <t>Sí, sin convenio ME</t>
-        </is>
-      </c>
-      <c r="Y31" s="4" t="n">
-        <v>9</v>
-      </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AA31" s="4" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AB31" s="4" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="AC31" t="inlineStr">
         <is>
@@ -6178,17 +6121,17 @@
       </c>
       <c r="AD31" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AE31" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AF31" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AG31" t="inlineStr">
@@ -6198,135 +6141,135 @@
       </c>
       <c r="AH31" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AJ31" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Centro Municipal Norte</t>
+          <t>Hogar Nuestra Señora</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Secretaría de Niñez, Adolescencia y Familia</t>
+          <t>Convenio con organización civil</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Barranqueras</t>
+          <t>Resistencia</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Belgrano 4812</t>
+          <t>Güemes 2307</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>11-4701-1339</t>
+          <t>11-4690-1659</t>
         </is>
       </c>
       <c r="F32" s="4" t="n">
         <v>56</v>
       </c>
       <c r="G32" s="4" t="n">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Sí, pero está desactualizado</t>
+          <t>Sí, está actualizado pero no se aplica</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No, pero se encuentra en diseño</t>
         </is>
       </c>
       <c r="J32" s="4" t="n">
-        <v>2</v>
+        <v>17</v>
       </c>
       <c r="K32" s="4" t="n">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="L32" s="4" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="M32" s="4" t="n">
+        <v>9</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="R32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="T32" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Sí, sin convenio ME</t>
+        </is>
+      </c>
+      <c r="W32" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="X32" t="inlineStr">
+        <is>
+          <t>Sí, sin convenio ME</t>
+        </is>
+      </c>
+      <c r="Y32" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="AA32" s="4" t="n">
         <v>6</v>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="R32" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="S32" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="T32" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W32" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="X32" t="inlineStr">
-        <is>
-          <t>Sí, con convenio ME</t>
-        </is>
-      </c>
-      <c r="Y32" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA32" s="4" t="n">
-        <v>14</v>
       </c>
       <c r="AB32" s="4" t="n">
         <v>11</v>
@@ -6343,17 +6286,17 @@
       </c>
       <c r="AE32" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AF32" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AG32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AH32" t="inlineStr">
@@ -6368,67 +6311,67 @@
       </c>
       <c r="AJ32" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Centro Municipal Norte</t>
+          <t>Programa de Acompañamiento Sur</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Servicio de Protección de Derechos</t>
+          <t>Secretaría de Niñez, Adolescencia y Familia</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Las Breñas</t>
+          <t>General San Martín</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Güemes 4606</t>
+          <t>Rivadavia 2748</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>11-4137-8451</t>
+          <t>11-4218-7622</t>
         </is>
       </c>
       <c r="F33" s="4" t="n">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="G33" s="4" t="n">
-        <v>28</v>
+        <v>60</v>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Sí, pero está desactualizado</t>
+          <t>Sí, es una herramienta de gestión</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Sí, pero está desactualizada</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J33" s="4" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="K33" s="4" t="n">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="L33" s="4" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="M33" s="4" t="n">
         <v>17</v>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -6438,12 +6381,12 @@
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -6461,35 +6404,35 @@
       </c>
       <c r="U33" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="V33" t="inlineStr">
         <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W33" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="X33" t="inlineStr">
+        <is>
           <t>Sí, sin convenio ME</t>
         </is>
       </c>
-      <c r="W33" s="4" t="n">
-        <v>20</v>
-      </c>
-      <c r="X33" t="inlineStr">
-        <is>
-          <t>Sí, sin convenio ME</t>
-        </is>
-      </c>
       <c r="Y33" s="4" t="n">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AA33" s="4" t="n">
-        <v>25</v>
+        <v>16</v>
       </c>
       <c r="AB33" s="4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
@@ -6498,7 +6441,7 @@
       </c>
       <c r="AD33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AE33" t="inlineStr">
@@ -6513,22 +6456,22 @@
       </c>
       <c r="AG33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AH33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AJ33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
     </row>
@@ -8748,64 +8691,64 @@
   </mergeCells>
   <dataValidations count="20">
     <dataValidation sqref="H4:H203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;¿Cuenta con Proyecto Institucional?&quot;." type="list">
-      <formula1>LISTAS!$C$2:$C$6</formula1>
+      <formula1>Listas!$C$2:$C$6</formula1>
     </dataValidation>
     <dataValidation sqref="I4:I203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;¿Cuenta con Normativa Convivencial?&quot;." type="list">
-      <formula1>LISTAS!$A$2:$A$6</formula1>
+      <formula1>Listas!$A$2:$A$6</formula1>
     </dataValidation>
     <dataValidation sqref="N4:N203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con protocolos de ingreso&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="O4:O203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con protocolo de requisa&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="P4:P203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con protocolo de denuncias por malos tratos&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="Q4:Q203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con protocolos de actuación ante conflictos entre pares&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="R4:R203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Protocolo de abordaje del suicidio&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="S4:S203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con protocolo de sanciones&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="U4:U203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con espacios para visitas socioafectivas&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="V4:V203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cumple con los niveles de obligatoriedad de educación primaria&quot;." type="list">
-      <formula1>LISTAS!$D$2:$D$4</formula1>
+      <formula1>Listas!$D$2:$D$4</formula1>
     </dataValidation>
     <dataValidation sqref="X4:X203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cumple con los niveles de obligatoriedad de educación secundaria&quot;." type="list">
-      <formula1>LISTAS!$D$2:$D$4</formula1>
+      <formula1>Listas!$D$2:$D$4</formula1>
     </dataValidation>
     <dataValidation sqref="Z4:Z203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Tiene aulas destinadas a la educación obligatoria&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="AC4:AC203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con espacio para talleres&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="AD4:AD203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con asesoramiento técnico jurídico&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="AE4:AE203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con patio abierto&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="AF4:AF203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con patio techado&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="AG4:AG203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con celdas secas&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="AH4:AH203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con celdas humedas&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="AI4:AI203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con mobiliario en las celdas&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="AJ4:AJ203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con colchones ignífugos&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9058,37 +9001,37 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Secretaría de Niñez, Adolescencia y Familia</t>
+          <t>Convenio con organización civil</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Villa Ángela</t>
+          <t>Las Breñas</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Alberdi 1397</t>
+          <t>San Martín 1940</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>11-4418-1224</t>
+          <t>11-4961-2858</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No, pero se encuentra en diseño</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>No, pero se encuentra en diseño</t>
+          <t>Sí, es una herramienta de gestión</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -9098,17 +9041,17 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
@@ -9117,38 +9060,38 @@
         </is>
       </c>
       <c r="N4" s="4" t="n">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="O4" s="4" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="P4" s="4" t="n">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="Q4" s="4" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="R4" s="4" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="S4" s="4" t="n">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="T4" s="4" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>Sí, sin convenio ME</t>
+          <t>Sí, con convenio ME</t>
         </is>
       </c>
       <c r="W4" s="4" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="X4" t="inlineStr">
         <is>
@@ -9156,7 +9099,7 @@
         </is>
       </c>
       <c r="Y4" s="4" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
@@ -9164,11 +9107,11 @@
         </is>
       </c>
       <c r="AA4" s="4" t="n">
+        <v>24</v>
+      </c>
+      <c r="AB4" s="4" t="n">
         <v>5</v>
       </c>
-      <c r="AB4" s="4" t="n">
-        <v>13</v>
-      </c>
       <c r="AC4" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -9176,32 +9119,32 @@
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -9223,42 +9166,42 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Charata</t>
+          <t>Quitilipi</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Güemes 121</t>
+          <t>Güemes 1317</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>11-4389-5891</t>
+          <t>11-4557-9824</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>No, pero se encuentra en diseño</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí, pero está desactualizada</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -9268,7 +9211,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -9277,128 +9220,128 @@
         </is>
       </c>
       <c r="N5" s="4" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="O5" s="4" t="n">
-        <v>29</v>
+        <v>52</v>
       </c>
       <c r="P5" s="4" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="Q5" s="4" t="n">
+        <v>19</v>
+      </c>
+      <c r="R5" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="S5" s="4" t="n">
+        <v>8</v>
+      </c>
+      <c r="T5" s="4" t="n">
         <v>25</v>
       </c>
-      <c r="R5" s="4" t="n">
-        <v>18</v>
-      </c>
-      <c r="S5" s="4" t="n">
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Sí, con convenio ME</t>
+        </is>
+      </c>
+      <c r="W5" s="4" t="n">
+        <v>11</v>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y5" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="AA5" s="4" t="n">
         <v>13</v>
       </c>
-      <c r="T5" s="4" t="n">
-        <v>15</v>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>Sí, con convenio ME</t>
-        </is>
-      </c>
-      <c r="W5" s="4" t="n">
-        <v>23</v>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>Sí, con convenio ME</t>
-        </is>
-      </c>
-      <c r="Y5" s="4" t="n">
-        <v>19</v>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="AA5" s="4" t="n">
-        <v>8</v>
-      </c>
       <c r="AB5" s="4" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Residencia El Ceibo</t>
+          <t>Centro Municipal Norte</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Municipalidad de Rawson</t>
+          <t>Secretaría de Niñez, Adolescencia y Familia</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Resistencia</t>
+          <t>Quitilipi</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Belgrano 4214</t>
+          <t>San Martín 4408</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>11-4704-6439</t>
+          <t>11-4567-1251</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Sí, es una herramienta de gestión</t>
+          <t>Sí, está actualizado pero no se aplica</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -9408,75 +9351,75 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="N6" s="4" t="n">
-        <v>34</v>
+        <v>47</v>
       </c>
       <c r="O6" s="4" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="P6" s="4" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="Q6" s="4" t="n">
+        <v>21</v>
+      </c>
+      <c r="R6" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="R6" s="4" t="n">
-        <v>16</v>
-      </c>
       <c r="S6" s="4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T6" s="4" t="n">
+        <v>22</v>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Sí, sin convenio ME</t>
+        </is>
+      </c>
+      <c r="W6" s="4" t="n">
         <v>11</v>
       </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Sin datos</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="W6" s="4" t="n">
-        <v>13</v>
-      </c>
       <c r="X6" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
       <c r="Y6" s="4" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
@@ -9484,24 +9427,24 @@
         </is>
       </c>
       <c r="AA6" s="4" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AB6" s="4" t="n">
-        <v>18</v>
+        <v>2</v>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -9511,12 +9454,12 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
@@ -9538,34 +9481,34 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ministerio de Desarrollo Social</t>
+          <t>Municipalidad de Rawson</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Charata</t>
+          <t>Barranqueras</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Belgrano 840</t>
+          <t>Güemes 923</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>11-4544-2612</t>
+          <t>11-4554-3725</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>Sí, pero está desactualizado</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>Sí, es una herramienta de gestión</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>No, pero se encuentra en diseño</t>
-        </is>
-      </c>
       <c r="H7" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -9573,22 +9516,22 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
@@ -9597,25 +9540,25 @@
         </is>
       </c>
       <c r="N7" s="4" t="n">
-        <v>58</v>
+        <v>35</v>
       </c>
       <c r="O7" s="4" t="n">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="P7" s="4" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Q7" s="4" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="R7" s="4" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="S7" s="4" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="T7" s="4" t="n">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="U7" t="inlineStr">
         <is>
@@ -9624,31 +9567,31 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí, con convenio ME</t>
         </is>
       </c>
       <c r="W7" s="4" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí, con convenio ME</t>
         </is>
       </c>
       <c r="Y7" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA7" s="4" t="n">
+        <v>20</v>
+      </c>
+      <c r="AB7" s="4" t="n">
         <v>22</v>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AA7" s="4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AB7" s="4" t="n">
-        <v>6</v>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
           <t>Sí</t>
@@ -9656,76 +9599,76 @@
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Residencia El Ceibo</t>
+          <t>Programa de Acompañamiento Sur</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ministerio de Desarrollo Social</t>
+          <t>Subsecretaría de Niñez y Adolescencia</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Quitilipi</t>
+          <t>Resistencia</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Alberdi 2180</t>
+          <t>Güemes 3911</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>11-4570-5183</t>
+          <t>11-4394-9955</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>Sí, está actualizado pero no se aplica</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
           <t>Sí, es una herramienta de gestión</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>No, pero se encuentra en diseño</t>
-        </is>
-      </c>
       <c r="H8" t="inlineStr">
         <is>
           <t>No</t>
@@ -9733,7 +9676,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -9743,12 +9686,12 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
@@ -9757,66 +9700,66 @@
         </is>
       </c>
       <c r="N8" s="4" t="n">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="O8" s="4" t="n">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="P8" s="4" t="n">
+        <v>15</v>
+      </c>
+      <c r="Q8" s="4" t="n">
         <v>10</v>
       </c>
-      <c r="Q8" s="4" t="n">
-        <v>21</v>
-      </c>
       <c r="R8" s="4" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="S8" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="T8" s="4" t="n">
+        <v>16</v>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Sí, con convenio ME</t>
+        </is>
+      </c>
+      <c r="W8" s="4" t="n">
+        <v>13</v>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="Y8" s="4" t="n">
+        <v>12</v>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>Sin datos</t>
+        </is>
+      </c>
+      <c r="AA8" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="AB8" s="4" t="n">
         <v>23</v>
       </c>
-      <c r="T8" s="4" t="n">
-        <v>9</v>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>Sí, sin convenio ME</t>
-        </is>
-      </c>
-      <c r="W8" s="4" t="n">
-        <v>7</v>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>Sí, sin convenio ME</t>
-        </is>
-      </c>
-      <c r="Y8" s="4" t="n">
-        <v>16</v>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Sí</t>
-        </is>
-      </c>
-      <c r="AA8" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="AB8" s="4" t="n">
-        <v>13</v>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
@@ -9831,17 +9774,17 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -9853,47 +9796,47 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Programa de Acompañamiento Sur</t>
+          <t>Hogar Los Álamos</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Subsecretaría de Niñez y Adolescencia</t>
+          <t>Convenio con organización civil</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Resistencia</t>
+          <t>Quitilipi</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Sarmiento 501</t>
+          <t>Güemes 2444</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>11-4720-9138</t>
+          <t>11-4894-4770</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sí, pero está desactualizado</t>
+          <t>No</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Sí, está actualizada pero no se aplica</t>
+          <t>Sí, pero está desactualizada</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -9908,7 +9851,7 @@
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -9917,25 +9860,25 @@
         </is>
       </c>
       <c r="N9" s="4" t="n">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="O9" s="4" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="P9" s="4" t="n">
         <v>25</v>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="R9" s="4" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="S9" s="4" t="n">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="U9" t="inlineStr">
         <is>
@@ -9948,30 +9891,30 @@
         </is>
       </c>
       <c r="W9" s="4" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí, con convenio ME</t>
         </is>
       </c>
       <c r="Y9" s="4" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AA9" s="4" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="AB9" s="4" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
@@ -9981,27 +9924,27 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>Sin datos</t>
+          <t>Sí</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Sin datos</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -10013,7 +9956,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Programa de Acompañamiento Sur</t>
+          <t>Residencia El Ceibo</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -10023,12 +9966,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Villa Ángela</t>
+          <t>Presidencia Roque Sáenz Peña</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Belgrano 4518</t>
+          <t>Güemes 4518</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -16066,64 +16009,64 @@
   </mergeCells>
   <dataValidations count="20">
     <dataValidation sqref="F4:F203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con Proyecto Institucional&quot;." type="list">
-      <formula1>LISTAS!$C$2:$C$6</formula1>
+      <formula1>Listas!$C$2:$C$6</formula1>
     </dataValidation>
     <dataValidation sqref="G4:G203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con Normativa Convivencial&quot;." type="list">
-      <formula1>LISTAS!$A$2:$A$6</formula1>
+      <formula1>Listas!$A$2:$A$6</formula1>
     </dataValidation>
     <dataValidation sqref="H4:H203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con protocolos de ingreso&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="I4:I203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con protocolo de requisa&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="J4:J203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con protocolo de denuncias por malos tratos&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="K4:K203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con protocolos de actuación ante conflictos entre pares&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="L4:L203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Protocolo de abordaje del suicidio&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="M4:M203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con protocolo de sanciones&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="U4:U203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con espacios para visitas socioafectivas&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="V4:V203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cumple con los niveles de obligatoriedad de educación primaria&quot;." type="list">
-      <formula1>LISTAS!$D$2:$D$4</formula1>
+      <formula1>Listas!$D$2:$D$4</formula1>
     </dataValidation>
     <dataValidation sqref="X4:X203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cumple con los niveles de obligatoriedad de educación secundaria&quot;." type="list">
-      <formula1>LISTAS!$D$2:$D$4</formula1>
+      <formula1>Listas!$D$2:$D$4</formula1>
     </dataValidation>
     <dataValidation sqref="Z4:Z203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Tiene aulas destinadas a la educación obligatoria&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="AC4:AC203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con espacio para talleres&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="AD4:AD203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con asesoramiento técnico jurídico&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="AE4:AE203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con patio abierto&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="AF4:AF203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con patio techado&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="AG4:AG203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con celdas secas&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="AH4:AH203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con celdas humedas&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="AI4:AI203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con mobiliario en las celdas&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="AJ4:AJ203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con colchones ignífugos&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -18228,13 +18171,13 @@
   </mergeCells>
   <dataValidations count="3">
     <dataValidation sqref="F4:F203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con Proyecto Institucional&quot;." type="list">
-      <formula1>LISTAS!$C$2:$C$6</formula1>
+      <formula1>Listas!$C$2:$C$6</formula1>
     </dataValidation>
     <dataValidation sqref="G4:G203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con espacio de grupalidad&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="I4:I203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con asesoramiento técnico jurídico&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -23651,46 +23594,46 @@
   </mergeCells>
   <dataValidations count="14">
     <dataValidation sqref="F4:F203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con Proyecto Institucional&quot;." type="list">
-      <formula1>LISTAS!$C$2:$C$6</formula1>
+      <formula1>Listas!$C$2:$C$6</formula1>
     </dataValidation>
     <dataValidation sqref="G4:G203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con resolución de creación&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="H4:H203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con Normativa Convivencial&quot;." type="list">
-      <formula1>LISTAS!$A$2:$A$6</formula1>
+      <formula1>Listas!$A$2:$A$6</formula1>
     </dataValidation>
     <dataValidation sqref="I4:I203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con protocolos de articulación interministerial. Con qué áreas&quot;." type="list">
-      <formula1>LISTAS!$B$2:$B$5</formula1>
+      <formula1>Listas!$B$2:$B$5</formula1>
     </dataValidation>
     <dataValidation sqref="J4:J203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con protocolos de ingreso&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="K4:K203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con protocolo de requisa&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="L4:L203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con protocolo de denuncias por malos tratos&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="M4:M203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con protocolos de actuación ante conflictos entre pares&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="N4:N203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con protocolo de abordaje del suicidio&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="O4:O203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con protocolo de sanciones&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="V4:V203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con celdas secas&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="W4:W203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con celdas humedas&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="X4:X203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con mobiliario en las celdas&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="Y4:Y203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con colchones ignífugos&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -25749,13 +25692,13 @@
   </mergeCells>
   <dataValidations count="3">
     <dataValidation sqref="D4:D203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con resolución de creación&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
     <dataValidation sqref="E4:E203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con protocolos de articulación interministerial. Con qué áreas&quot;." type="list">
-      <formula1>LISTAS!$B$2:$B$5</formula1>
+      <formula1>Listas!$B$2:$B$5</formula1>
     </dataValidation>
     <dataValidation sqref="F4:F203" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Valor no admitido" error="El valor no está entre los admitidos para &quot;Cuenta con protocolo de denuncias por malos tratos&quot;." type="list">
-      <formula1>LISTAS!$E$2:$E$4</formula1>
+      <formula1>Listas!$E$2:$E$4</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -25764,1275 +25707,6 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:B128"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="95" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>Campo</t>
-        </is>
-      </c>
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>Indicación para el llenado</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>Hoja: CRC</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Nombre del dispositvo</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>Campo obligatorio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Dependencia institucional</t>
-        </is>
-      </c>
-      <c r="B4" s="7" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Localidad</t>
-        </is>
-      </c>
-      <c r="B5" s="7" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Dirección</t>
-        </is>
-      </c>
-      <c r="B6" s="7" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Teléfono</t>
-        </is>
-      </c>
-      <c r="B7" s="7" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Capacidad de alojamiento mujeres (plazas disponibles)</t>
-        </is>
-      </c>
-      <c r="B8" s="7" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Capacidad de alojamiento varones (plazas disponibles)</t>
-        </is>
-      </c>
-      <c r="B9" s="7" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>¿Cuenta con Proyecto Institucional?</t>
-        </is>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Cuenta con Proyecto Institucional".</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>¿Cuenta con Normativa Convivencial?</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Cuenta con Normativa Convivencial".</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Cantidad de agentes: equipo técnico y profesional (incluye cuidadores)</t>
-        </is>
-      </c>
-      <c r="B12" s="7" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Cantidad agentes de salud</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Cantidad de personal: administrativo, limpieza, cocina y mantenimiento</t>
-        </is>
-      </c>
-      <c r="B14" s="7" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Cantidad de personal seguridad</t>
-        </is>
-      </c>
-      <c r="B15" s="7" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Cuenta con protocolos de ingreso</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Cuenta con protocolo de requisa</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Cuenta con protocolo de denuncias por malos tratos</t>
-        </is>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Cuenta con protocolos de actuación ante conflictos entre pares</t>
-        </is>
-      </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Protocolo de abordaje del suicidio</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Cuenta con protocolo de sanciones</t>
-        </is>
-      </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>Cantidad de horas semanales destinadas al contacto presencial, afectivo/familiar</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="n"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>Cuenta con espacios para visitas socioafectivas</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>Cumple con los niveles de obligatoriedad de educación primaria</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Cumple con los niveles de obligatoriedad de educación primaria".</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Cantidad de horas semanales dedicadas a la educación primaria</t>
-        </is>
-      </c>
-      <c r="B25" s="7" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Cumple con los niveles de obligatoriedad de educación secundaria</t>
-        </is>
-      </c>
-      <c r="B26" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Cumple con los niveles de obligatoriedad de educación primaria".</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Cantidad de horas semanales dedicadas a la educación secundaria</t>
-        </is>
-      </c>
-      <c r="B27" s="7" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Tiene aulas destinadas a la educación obligatoria</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Cantidad de horas semanales dedicadas a la formación profesional</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Cantidad de horas semanales dedicadas a talleres deportivos y culturales</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Cuenta con espacio para talleres</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Cuenta con asesoramiento técnico jurídico</t>
-        </is>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Cuenta con patio abierto</t>
-        </is>
-      </c>
-      <c r="B33" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Cuenta con patio techado</t>
-        </is>
-      </c>
-      <c r="B34" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Cuenta con celdas secas</t>
-        </is>
-      </c>
-      <c r="B35" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Cuenta con celdas humedas</t>
-        </is>
-      </c>
-      <c r="B36" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Cuenta con mobiliario en las celdas</t>
-        </is>
-      </c>
-      <c r="B37" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Cuenta con colchones ignífugos</t>
-        </is>
-      </c>
-      <c r="B38" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="6" t="inlineStr">
-        <is>
-          <t>Hoja: CRSC</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Nombre del dispositvo</t>
-        </is>
-      </c>
-      <c r="B41" s="7" t="inlineStr">
-        <is>
-          <t>Campo obligatorio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Dependencia institucional</t>
-        </is>
-      </c>
-      <c r="B42" s="7" t="n"/>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Localidad</t>
-        </is>
-      </c>
-      <c r="B43" s="7" t="n"/>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Dirección</t>
-        </is>
-      </c>
-      <c r="B44" s="7" t="n"/>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Teléfono</t>
-        </is>
-      </c>
-      <c r="B45" s="7" t="n"/>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Cuenta con Proyecto Institucional</t>
-        </is>
-      </c>
-      <c r="B46" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Cuenta con Proyecto Institucional".</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>Cuenta con Normativa Convivencial</t>
-        </is>
-      </c>
-      <c r="B47" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Cuenta con Normativa Convivencial".</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Cuenta con protocolos de ingreso</t>
-        </is>
-      </c>
-      <c r="B48" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Cuenta con protocolo de requisa</t>
-        </is>
-      </c>
-      <c r="B49" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Cuenta con protocolo de denuncias por malos tratos</t>
-        </is>
-      </c>
-      <c r="B50" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>Cuenta con protocolos de actuación ante conflictos entre pares</t>
-        </is>
-      </c>
-      <c r="B51" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Protocolo de abordaje del suicidio</t>
-        </is>
-      </c>
-      <c r="B52" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>Cuenta con protocolo de sanciones</t>
-        </is>
-      </c>
-      <c r="B53" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Capacidad de alojamiento mujeres (plazas disponibles)</t>
-        </is>
-      </c>
-      <c r="B54" s="7" t="n"/>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Capacidad de alojamiento varones (plazas disponibles)</t>
-        </is>
-      </c>
-      <c r="B55" s="7" t="n"/>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Cantidad de agentes: equipo técnico y profesional (incluye cuidadores)</t>
-        </is>
-      </c>
-      <c r="B56" s="7" t="n"/>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Cantidad agentes de salud</t>
-        </is>
-      </c>
-      <c r="B57" s="7" t="n"/>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Cantidad de personal: administrativo, limpieza, cocina y mantenimiento</t>
-        </is>
-      </c>
-      <c r="B58" s="7" t="n"/>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>Cantidad de personal seguridad</t>
-        </is>
-      </c>
-      <c r="B59" s="7" t="n"/>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Cantidad de horas semanales destinadas al contacto presencial, afectivo/familiar</t>
-        </is>
-      </c>
-      <c r="B60" s="7" t="n"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Cuenta con espacios para visitas socioafectivas</t>
-        </is>
-      </c>
-      <c r="B61" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Cumple con los niveles de obligatoriedad de educación primaria</t>
-        </is>
-      </c>
-      <c r="B62" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Cumple con los niveles de obligatoriedad de educación primaria".</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Cantidad de horas semanales dedicadas a la educación primaria</t>
-        </is>
-      </c>
-      <c r="B63" s="7" t="n"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Cumple con los niveles de obligatoriedad de educación secundaria</t>
-        </is>
-      </c>
-      <c r="B64" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Cumple con los niveles de obligatoriedad de educación primaria".</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Cantidad de horas semanales dedicadas a la educación secundaria</t>
-        </is>
-      </c>
-      <c r="B65" s="7" t="n"/>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Tiene aulas destinadas a la educación obligatoria</t>
-        </is>
-      </c>
-      <c r="B66" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Cantidad de horas semanales dedicadas a la formación profesional</t>
-        </is>
-      </c>
-      <c r="B67" s="7" t="n"/>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>Cantidad de horas semanales dedicadas a talleres deportivos y culturales</t>
-        </is>
-      </c>
-      <c r="B68" s="7" t="n"/>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>Cuenta con espacio para talleres</t>
-        </is>
-      </c>
-      <c r="B69" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Cuenta con asesoramiento técnico jurídico</t>
-        </is>
-      </c>
-      <c r="B70" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Cuenta con patio abierto</t>
-        </is>
-      </c>
-      <c r="B71" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Cuenta con patio techado</t>
-        </is>
-      </c>
-      <c r="B72" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Cuenta con celdas secas</t>
-        </is>
-      </c>
-      <c r="B73" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Cuenta con celdas humedas</t>
-        </is>
-      </c>
-      <c r="B74" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Cuenta con mobiliario en las celdas</t>
-        </is>
-      </c>
-      <c r="B75" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Cuenta con colchones ignífugos</t>
-        </is>
-      </c>
-      <c r="B76" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="6" t="inlineStr">
-        <is>
-          <t>Hoja: MPT</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>Nombre del dispositvo</t>
-        </is>
-      </c>
-      <c r="B79" s="7" t="inlineStr">
-        <is>
-          <t>Campo obligatorio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Dependencia institucional</t>
-        </is>
-      </c>
-      <c r="B80" s="7" t="n"/>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Localidad</t>
-        </is>
-      </c>
-      <c r="B81" s="7" t="n"/>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Dirección</t>
-        </is>
-      </c>
-      <c r="B82" s="7" t="n"/>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Teléfono</t>
-        </is>
-      </c>
-      <c r="B83" s="7" t="n"/>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Cuenta con Proyecto Institucional</t>
-        </is>
-      </c>
-      <c r="B84" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Cuenta con Proyecto Institucional".</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Cuenta con espacio de grupalidad</t>
-        </is>
-      </c>
-      <c r="B85" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Cantidad de agentes: equipo técnico y profesional (incluye cuidadores)</t>
-        </is>
-      </c>
-      <c r="B86" s="7" t="n"/>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Cuenta con asesoramiento técnico jurídico</t>
-        </is>
-      </c>
-      <c r="B87" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Jurisdicciones dentro de la provincia en las que el dispositivo tiene alcance</t>
-        </is>
-      </c>
-      <c r="B88" s="7" t="n"/>
-    </row>
-    <row r="90">
-      <c r="A90" s="6" t="inlineStr">
-        <is>
-          <t>Hoja: CAD</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Nombre del dispositvo</t>
-        </is>
-      </c>
-      <c r="B91" s="7" t="inlineStr">
-        <is>
-          <t>Campo obligatorio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Dependencia institucional</t>
-        </is>
-      </c>
-      <c r="B92" s="7" t="n"/>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Localidad</t>
-        </is>
-      </c>
-      <c r="B93" s="7" t="n"/>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Dirección</t>
-        </is>
-      </c>
-      <c r="B94" s="7" t="n"/>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Teléfono</t>
-        </is>
-      </c>
-      <c r="B95" s="7" t="n"/>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Cuenta con Proyecto Institucional</t>
-        </is>
-      </c>
-      <c r="B96" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Cuenta con Proyecto Institucional".</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Cuenta con resolución de creación</t>
-        </is>
-      </c>
-      <c r="B97" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Cuenta con Normativa Convivencial</t>
-        </is>
-      </c>
-      <c r="B98" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Cuenta con Normativa Convivencial".</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Cuenta con protocolos de articulación interministerial. Con qué áreas</t>
-        </is>
-      </c>
-      <c r="B99" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Cuenta con protocolos de articulación interministerial. Con qué áreas".</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Cuenta con protocolos de ingreso</t>
-        </is>
-      </c>
-      <c r="B100" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Cuenta con protocolo de requisa</t>
-        </is>
-      </c>
-      <c r="B101" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Cuenta con protocolo de denuncias por malos tratos</t>
-        </is>
-      </c>
-      <c r="B102" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Cuenta con protocolos de actuación ante conflictos entre pares</t>
-        </is>
-      </c>
-      <c r="B103" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Cuenta con protocolo de abordaje del suicidio</t>
-        </is>
-      </c>
-      <c r="B104" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Cuenta con protocolo de sanciones</t>
-        </is>
-      </c>
-      <c r="B105" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Capacidad de alojamiento mujeres (plazas disponibles)</t>
-        </is>
-      </c>
-      <c r="B106" s="7" t="n"/>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Capacidad de alojamiento varones (plazas disponibles)</t>
-        </is>
-      </c>
-      <c r="B107" s="7" t="n"/>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Cantidad de agentes: equipo técnico y profesional (incluye cuidadores)</t>
-        </is>
-      </c>
-      <c r="B108" s="7" t="n"/>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Cantidad agentes de salud</t>
-        </is>
-      </c>
-      <c r="B109" s="7" t="n"/>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Cantidad de personal: administrativo, limpieza, cocina y mantenimiento</t>
-        </is>
-      </c>
-      <c r="B110" s="7" t="n"/>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Cantidad de personal seguridad</t>
-        </is>
-      </c>
-      <c r="B111" s="7" t="n"/>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Cuenta con celdas secas</t>
-        </is>
-      </c>
-      <c r="B112" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Cuenta con celdas humedas</t>
-        </is>
-      </c>
-      <c r="B113" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Cuenta con mobiliario en las celdas</t>
-        </is>
-      </c>
-      <c r="B114" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Cuenta con colchones ignífugos</t>
-        </is>
-      </c>
-      <c r="B115" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Jurisdicciones dentro de la provincia en las que tiene alcancce territorial el dispositivo</t>
-        </is>
-      </c>
-      <c r="B116" s="7" t="n"/>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Tiempo máximo de permanencia dentro del dispositivo (en horas)</t>
-        </is>
-      </c>
-      <c r="B117" s="7" t="n"/>
-    </row>
-    <row r="119">
-      <c r="A119" s="6" t="inlineStr">
-        <is>
-          <t>Hoja: Guardia Comisaría</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Nombre del dispositvo</t>
-        </is>
-      </c>
-      <c r="B120" s="7" t="inlineStr">
-        <is>
-          <t>Campo obligatorio.</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Dependencia institucional</t>
-        </is>
-      </c>
-      <c r="B121" s="7" t="n"/>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Teléfono</t>
-        </is>
-      </c>
-      <c r="B122" s="7" t="n"/>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Cuenta con resolución de creación</t>
-        </is>
-      </c>
-      <c r="B123" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Cuenta con protocolos de articulación interministerial. Con qué áreas</t>
-        </is>
-      </c>
-      <c r="B124" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Cuenta con protocolos de articulación interministerial. Con qué áreas".</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Cuenta con protocolo de denuncias por malos tratos</t>
-        </is>
-      </c>
-      <c r="B125" s="7" t="inlineStr">
-        <is>
-          <t>Debe elegirse un valor de la lista "Sí / No / Sin datos".</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Cantidad de agentes: equipo técnico y profesional (incluye cuidadores)</t>
-        </is>
-      </c>
-      <c r="B126" s="7" t="n"/>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Jurisdicciones dentro de la provincia en las que tiene alcancce territorial el dispositivo</t>
-        </is>
-      </c>
-      <c r="B127" s="7" t="n"/>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Tiempo máximo de permanencia dentro del dispositivo (en horas)</t>
-        </is>
-      </c>
-      <c r="B128" s="7" t="n"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
